--- a/docs/测试用例表.xlsx
+++ b/docs/测试用例表.xlsx
@@ -596,7 +596,7 @@
       <c r="I2" s="7" t="inlineStr"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       <c r="I3" s="7" t="inlineStr"/>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       <c r="I4" s="7" t="inlineStr"/>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       <c r="I6" s="7" t="inlineStr"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       <c r="I10" s="7" t="inlineStr"/>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       <c r="I11" s="7" t="inlineStr"/>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       <c r="I12" s="7" t="inlineStr"/>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       <c r="I26" s="7" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       <c r="I27" s="7" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       <c r="I28" s="7" t="inlineStr"/>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       <c r="I30" s="7" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       <c r="I44" s="7" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       <c r="I48" s="7" t="inlineStr"/>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="I52" s="7" t="inlineStr"/>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       <c r="I54" s="7" t="inlineStr"/>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       <c r="I56" s="7" t="inlineStr"/>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       <c r="I59" s="7" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       <c r="I61" s="7" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       <c r="I63" s="7" t="inlineStr"/>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       <c r="I64" s="7" t="inlineStr"/>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       <c r="I66" s="7" t="inlineStr"/>
       <c r="J66" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       <c r="I72" s="7" t="inlineStr"/>
       <c r="J72" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票创建功能</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票创建功能</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票创建功能</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票列表功能</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票列表功能</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       <c r="I81" s="7" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票详情功能</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       <c r="I82" s="8" t="inlineStr"/>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>mock-server正确返回404</t>
+          <t>投票不存在应返回404 - mock-server正确处理</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       <c r="I84" s="7" t="inlineStr"/>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4036,7 @@
       <c r="I88" s="7" t="inlineStr"/>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/votes不存在</t>
+          <t>后端无投票功能</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="I90" s="7" t="inlineStr"/>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       <c r="I92" s="7" t="inlineStr"/>
       <c r="J92" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       <c r="I93" s="7" t="inlineStr"/>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       <c r="I94" s="7" t="inlineStr"/>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4316,7 @@
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       <c r="I96" s="7" t="inlineStr"/>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       <c r="I97" s="7" t="inlineStr"/>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>jest.skip()不可用</t>
+          <t>后端无评价配置功能</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       <c r="I98" s="7" t="inlineStr"/>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价提交功能</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       <c r="I99" s="7" t="inlineStr"/>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价提交功能</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       <c r="I100" s="7" t="inlineStr"/>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价提交功能</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       <c r="I101" s="7" t="inlineStr"/>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价提交功能</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       <c r="I102" s="7" t="inlineStr"/>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价提交功能</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       <c r="I103" s="7" t="inlineStr"/>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价统计功能</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       <c r="I104" s="7" t="inlineStr"/>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价统计功能</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       <c r="I105" s="7" t="inlineStr"/>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价统计功能</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       <c r="I106" s="7" t="inlineStr"/>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>404 - 路由/api/rating-categories不存在</t>
+          <t>后端无评价统计功能</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       <c r="I107" s="7" t="inlineStr"/>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       <c r="I108" s="7" t="inlineStr"/>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       <c r="I109" s="7" t="inlineStr"/>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       <c r="I110" s="7" t="inlineStr"/>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       <c r="I111" s="7" t="inlineStr"/>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       <c r="I112" s="7" t="inlineStr"/>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="I113" s="7" t="inlineStr"/>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       <c r="I115" s="7" t="inlineStr"/>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       <c r="I116" s="7" t="inlineStr"/>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       <c r="I117" s="7" t="inlineStr"/>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       <c r="I118" s="7" t="inlineStr"/>
       <c r="J118" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       <c r="I119" s="7" t="inlineStr"/>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       <c r="I120" s="7" t="inlineStr"/>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       <c r="I121" s="7" t="inlineStr"/>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -5396,2407 +5396,2407 @@
       <c r="I122" s="7" t="inlineStr"/>
       <c r="J122" s="7" t="inlineStr">
         <is>
-          <t>连接7001失败，服务未运行</t>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>MG-001</t>
         </is>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C123" s="9" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>页面Header渲染</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E123" s="9" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>页面含"🏠 家园"和副标题</t>
         </is>
       </c>
-      <c r="F123" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G123" s="9" t="inlineStr"/>
-      <c r="H123" s="9" t="inlineStr"/>
-      <c r="I123" s="9" t="inlineStr"/>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="7" t="inlineStr"/>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>MG-002</t>
         </is>
       </c>
-      <c r="B124" s="9" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>Tab切换渲染</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E124" s="9" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>页面含"按楼栋"和"小区总榜"</t>
         </is>
       </c>
-      <c r="F124" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G124" s="9" t="inlineStr"/>
-      <c r="H124" s="9" t="inlineStr"/>
-      <c r="I124" s="9" t="inlineStr"/>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr"/>
+      <c r="I124" s="7" t="inlineStr"/>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>MG-003</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>默认显示楼栋视角</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E125" s="9" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>页面含"A栋"</t>
         </is>
       </c>
-      <c r="F125" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr"/>
-      <c r="I125" s="9" t="inlineStr"/>
-      <c r="J125" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr"/>
+      <c r="H125" s="7" t="inlineStr"/>
+      <c r="I125" s="7" t="inlineStr"/>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>MG-004</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C126" s="9" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>Mock数据渲染楼栋列表</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E126" s="9" t="inlineStr">
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>页面含"B栋"和"C栋"</t>
         </is>
       </c>
-      <c r="F126" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G126" s="9" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr"/>
-      <c r="I126" s="9" t="inlineStr"/>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+      <c r="H126" s="7" t="inlineStr"/>
+      <c r="I126" s="7" t="inlineStr"/>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>MG-005</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>楼栋总积分显示</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D127" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E127" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 总积分 1250"等</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr"/>
-      <c r="I127" s="9" t="inlineStr"/>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr"/>
+      <c r="I127" s="7" t="inlineStr"/>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>MG-006</t>
         </is>
       </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>Top3贡献者显示</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E128" s="9" t="inlineStr">
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>页面含"张三""李四""王五"</t>
         </is>
       </c>
-      <c r="F128" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr"/>
-      <c r="I128" s="9" t="inlineStr"/>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr"/>
+      <c r="H128" s="7" t="inlineStr"/>
+      <c r="I128" s="7" t="inlineStr"/>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>MG-007</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>贡献积分显示</t>
         </is>
       </c>
-      <c r="D129" s="9" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E129" s="9" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>页面含"+320分"等</t>
         </is>
       </c>
-      <c r="F129" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr"/>
-      <c r="I129" s="9" t="inlineStr"/>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr"/>
+      <c r="I129" s="7" t="inlineStr"/>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>MG-008</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
         <is>
           <t>贡献等级星级显示</t>
         </is>
       </c>
-      <c r="D130" s="9" t="inlineStr">
+      <c r="D130" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E130" s="9" t="inlineStr">
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t>页面含"★★★"和"★★"</t>
         </is>
       </c>
-      <c r="F130" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr"/>
-      <c r="I130" s="9" t="inlineStr"/>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr"/>
+      <c r="H130" s="7" t="inlineStr"/>
+      <c r="I130" s="7" t="inlineStr"/>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>MG-009</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>排名徽章显示</t>
         </is>
       </c>
-      <c r="D131" s="9" t="inlineStr">
+      <c r="D131" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E131" s="9" t="inlineStr">
+      <c r="E131" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-badge元素</t>
         </is>
       </c>
-      <c r="F131" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr"/>
-      <c r="I131" s="9" t="inlineStr"/>
-      <c r="J131" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr"/>
+      <c r="I131" s="7" t="inlineStr"/>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>MG-010</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>Tab切换-小区总榜</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>页面显示"绿城花园"</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr"/>
-      <c r="I132" s="9" t="inlineStr"/>
-      <c r="J132" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr"/>
+      <c r="I132" s="7" t="inlineStr"/>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>MG-011</t>
         </is>
       </c>
-      <c r="B133" s="9" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>小区总榜-社区总积分</t>
         </is>
       </c>
-      <c r="D133" s="9" t="inlineStr">
+      <c r="D133" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E133" s="9" t="inlineStr">
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 社区总贡献积分"</t>
         </is>
       </c>
-      <c r="F133" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr"/>
-      <c r="I133" s="9" t="inlineStr"/>
-      <c r="J133" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr"/>
+      <c r="I133" s="7" t="inlineStr"/>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>MG-012</t>
         </is>
       </c>
-      <c r="B134" s="9" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>小区总榜-Top10住户</t>
         </is>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr">
+      <c r="E134" s="7" t="inlineStr">
         <is>
           <t>页面含"陈十四""张三"等</t>
         </is>
       </c>
-      <c r="F134" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr"/>
-      <c r="I134" s="9" t="inlineStr"/>
-      <c r="J134" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr"/>
+      <c r="H134" s="7" t="inlineStr"/>
+      <c r="I134" s="7" t="inlineStr"/>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t>MG-013</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>Tab切回楼栋视角</t>
         </is>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("按楼栋")</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr">
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>页面显示"A栋"，不含"绿城花园"</t>
         </is>
       </c>
-      <c r="F135" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="inlineStr"/>
-      <c r="H135" s="9" t="inlineStr"/>
-      <c r="I135" s="9" t="inlineStr"/>
-      <c r="J135" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="7" t="inlineStr"/>
+      <c r="I135" s="7" t="inlineStr"/>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>MG-014</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
         <is>
           <t>楼栋展开</t>
         </is>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)</t>
         </is>
       </c>
-      <c r="E136" s="9" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t>页面显示"赵六"</t>
         </is>
       </c>
-      <c r="F136" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G136" s="9" t="inlineStr"/>
-      <c r="H136" s="9" t="inlineStr"/>
-      <c r="I136" s="9" t="inlineStr"/>
-      <c r="J136" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr"/>
+      <c r="H136" s="7" t="inlineStr"/>
+      <c r="I136" s="7" t="inlineStr"/>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>MG-015</t>
         </is>
       </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>楼栋折叠</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)两次</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>页面不显示"赵六"</t>
         </is>
       </c>
-      <c r="F137" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr"/>
-      <c r="H137" s="9" t="inlineStr"/>
-      <c r="I137" s="9" t="inlineStr"/>
-      <c r="J137" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr"/>
+      <c r="H137" s="7" t="inlineStr"/>
+      <c r="I137" s="7" t="inlineStr"/>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="inlineStr">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>MG-016</t>
         </is>
       </c>
-      <c r="B138" s="9" t="inlineStr">
+      <c r="B138" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C138" s="7" t="inlineStr">
         <is>
           <t>空数据不崩溃</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
         <is>
           <t>render with empty data</t>
         </is>
       </c>
-      <c r="E138" s="9" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t>页面不崩溃，含garden-page根元素</t>
         </is>
       </c>
-      <c r="F138" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G138" s="9" t="inlineStr"/>
-      <c r="H138" s="9" t="inlineStr"/>
-      <c r="I138" s="9" t="inlineStr"/>
-      <c r="J138" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr"/>
+      <c r="H138" s="7" t="inlineStr"/>
+      <c r="I138" s="7" t="inlineStr"/>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>MG-017</t>
         </is>
       </c>
-      <c r="B139" s="9" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C139" s="9" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>楼栋渲染数量</t>
         </is>
       </c>
-      <c r="D139" s="9" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E139" s="9" t="inlineStr">
+      <c r="E139" s="7" t="inlineStr">
         <is>
           <t>building-card数量=3</t>
         </is>
       </c>
-      <c r="F139" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G139" s="9" t="inlineStr"/>
-      <c r="H139" s="9" t="inlineStr"/>
-      <c r="I139" s="9" t="inlineStr"/>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr"/>
+      <c r="H139" s="7" t="inlineStr"/>
+      <c r="I139" s="7" t="inlineStr"/>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>MG-018</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
         <is>
           <t>小区Banner渲染</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E140" s="9" t="inlineStr">
+      <c r="E140" s="7" t="inlineStr">
         <is>
           <t>页面含.community-banner</t>
         </is>
       </c>
-      <c r="F140" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr"/>
-      <c r="H140" s="9" t="inlineStr"/>
-      <c r="I140" s="9" t="inlineStr"/>
-      <c r="J140" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr"/>
+      <c r="H140" s="7" t="inlineStr"/>
+      <c r="I140" s="7" t="inlineStr"/>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>MG-019</t>
         </is>
       </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>排名列表渲染</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E141" s="9" t="inlineStr">
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-list</t>
         </is>
       </c>
-      <c r="F141" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr"/>
-      <c r="H141" s="9" t="inlineStr"/>
-      <c r="I141" s="9" t="inlineStr"/>
-      <c r="J141" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr"/>
+      <c r="I141" s="7" t="inlineStr"/>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>MG-020</t>
         </is>
       </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>排名列表记录数</t>
         </is>
       </c>
-      <c r="D142" s="9" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E142" s="9" t="inlineStr">
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t>resident-row数量=10</t>
         </is>
       </c>
-      <c r="F142" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr"/>
-      <c r="H142" s="9" t="inlineStr"/>
-      <c r="I142" s="9" t="inlineStr"/>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr"/>
+      <c r="H142" s="7" t="inlineStr"/>
+      <c r="I142" s="7" t="inlineStr"/>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>MG-001</t>
         </is>
       </c>
-      <c r="B143" s="9" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>页面Header渲染</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E143" s="9" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>页面含"🏠 家园"和副标题</t>
         </is>
       </c>
-      <c r="F143" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G143" s="9" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr"/>
-      <c r="I143" s="9" t="inlineStr"/>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
+      <c r="H143" s="7" t="inlineStr"/>
+      <c r="I143" s="7" t="inlineStr"/>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>MG-002</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>Tab切换渲染</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="E144" s="7" t="inlineStr">
         <is>
           <t>页面含"按楼栋"和"小区总榜"</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G144" s="9" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr"/>
-      <c r="I144" s="9" t="inlineStr"/>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr"/>
+      <c r="I144" s="7" t="inlineStr"/>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>MG-003</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>默认显示楼栋视角</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t>页面含"A栋"</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr"/>
-      <c r="I145" s="9" t="inlineStr"/>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr"/>
+      <c r="I145" s="7" t="inlineStr"/>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>MG-004</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>Mock数据渲染楼栋列表</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E146" s="9" t="inlineStr">
+      <c r="E146" s="7" t="inlineStr">
         <is>
           <t>页面含"B栋"和"C栋"</t>
         </is>
       </c>
-      <c r="F146" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr"/>
-      <c r="I146" s="9" t="inlineStr"/>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr"/>
+      <c r="H146" s="7" t="inlineStr"/>
+      <c r="I146" s="7" t="inlineStr"/>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="9" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>MG-005</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C147" s="7" t="inlineStr">
         <is>
           <t>楼栋总积分显示</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D147" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
+      <c r="E147" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 总积分 1250"等</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr"/>
-      <c r="I147" s="9" t="inlineStr"/>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr"/>
+      <c r="H147" s="7" t="inlineStr"/>
+      <c r="I147" s="7" t="inlineStr"/>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>MG-006</t>
         </is>
       </c>
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
         <is>
           <t>Top3贡献者显示</t>
         </is>
       </c>
-      <c r="D148" s="9" t="inlineStr">
+      <c r="D148" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E148" s="9" t="inlineStr">
+      <c r="E148" s="7" t="inlineStr">
         <is>
           <t>页面含"张三""李四""王五"</t>
         </is>
       </c>
-      <c r="F148" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr"/>
-      <c r="H148" s="9" t="inlineStr"/>
-      <c r="I148" s="9" t="inlineStr"/>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr"/>
+      <c r="H148" s="7" t="inlineStr"/>
+      <c r="I148" s="7" t="inlineStr"/>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="9" t="inlineStr">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t>MG-007</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>贡献积分显示</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E149" s="9" t="inlineStr">
+      <c r="E149" s="7" t="inlineStr">
         <is>
           <t>页面含"+320分"等</t>
         </is>
       </c>
-      <c r="F149" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr"/>
-      <c r="H149" s="9" t="inlineStr"/>
-      <c r="I149" s="9" t="inlineStr"/>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr"/>
+      <c r="H149" s="7" t="inlineStr"/>
+      <c r="I149" s="7" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="inlineStr">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>MG-008</t>
         </is>
       </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>贡献等级星级显示</t>
         </is>
       </c>
-      <c r="D150" s="9" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E150" s="9" t="inlineStr">
+      <c r="E150" s="7" t="inlineStr">
         <is>
           <t>页面含"★★★"和"★★"</t>
         </is>
       </c>
-      <c r="F150" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr"/>
-      <c r="H150" s="9" t="inlineStr"/>
-      <c r="I150" s="9" t="inlineStr"/>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr"/>
+      <c r="H150" s="7" t="inlineStr"/>
+      <c r="I150" s="7" t="inlineStr"/>
+      <c r="J150" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t>MG-009</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>排名徽章显示</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D151" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="E151" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-badge元素</t>
         </is>
       </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr"/>
-      <c r="I151" s="9" t="inlineStr"/>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr"/>
+      <c r="H151" s="7" t="inlineStr"/>
+      <c r="I151" s="7" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="9" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>MG-010</t>
         </is>
       </c>
-      <c r="B152" s="9" t="inlineStr">
+      <c r="B152" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="C152" s="7" t="inlineStr">
         <is>
           <t>Tab切换-小区总榜</t>
         </is>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D152" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E152" s="9" t="inlineStr">
+      <c r="E152" s="7" t="inlineStr">
         <is>
           <t>页面显示"绿城花园"</t>
         </is>
       </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr"/>
-      <c r="I152" s="9" t="inlineStr"/>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr"/>
+      <c r="H152" s="7" t="inlineStr"/>
+      <c r="I152" s="7" t="inlineStr"/>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>MG-011</t>
         </is>
       </c>
-      <c r="B153" s="9" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="C153" s="7" t="inlineStr">
         <is>
           <t>小区总榜-社区总积分</t>
         </is>
       </c>
-      <c r="D153" s="9" t="inlineStr">
+      <c r="D153" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E153" s="9" t="inlineStr">
+      <c r="E153" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 社区总贡献积分"</t>
         </is>
       </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr"/>
-      <c r="H153" s="9" t="inlineStr"/>
-      <c r="I153" s="9" t="inlineStr"/>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr"/>
+      <c r="H153" s="7" t="inlineStr"/>
+      <c r="I153" s="7" t="inlineStr"/>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="inlineStr">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>MG-012</t>
         </is>
       </c>
-      <c r="B154" s="9" t="inlineStr">
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C154" s="7" t="inlineStr">
         <is>
           <t>小区总榜-Top10住户</t>
         </is>
       </c>
-      <c r="D154" s="9" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E154" s="9" t="inlineStr">
+      <c r="E154" s="7" t="inlineStr">
         <is>
           <t>页面含"陈十四""张三"等</t>
         </is>
       </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr"/>
-      <c r="H154" s="9" t="inlineStr"/>
-      <c r="I154" s="9" t="inlineStr"/>
-      <c r="J154" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr"/>
+      <c r="H154" s="7" t="inlineStr"/>
+      <c r="I154" s="7" t="inlineStr"/>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="inlineStr">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>MG-013</t>
         </is>
       </c>
-      <c r="B155" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>Tab切回楼栋视角</t>
         </is>
       </c>
-      <c r="D155" s="9" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("按楼栋")</t>
         </is>
       </c>
-      <c r="E155" s="9" t="inlineStr">
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>页面显示"A栋"，不含"绿城花园"</t>
         </is>
       </c>
-      <c r="F155" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr"/>
-      <c r="H155" s="9" t="inlineStr"/>
-      <c r="I155" s="9" t="inlineStr"/>
-      <c r="J155" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr"/>
+      <c r="H155" s="7" t="inlineStr"/>
+      <c r="I155" s="7" t="inlineStr"/>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="9" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>MG-014</t>
         </is>
       </c>
-      <c r="B156" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
         <is>
           <t>楼栋展开</t>
         </is>
       </c>
-      <c r="D156" s="9" t="inlineStr">
+      <c r="D156" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)</t>
         </is>
       </c>
-      <c r="E156" s="9" t="inlineStr">
+      <c r="E156" s="7" t="inlineStr">
         <is>
           <t>页面显示"赵六"</t>
         </is>
       </c>
-      <c r="F156" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G156" s="9" t="inlineStr"/>
-      <c r="H156" s="9" t="inlineStr"/>
-      <c r="I156" s="9" t="inlineStr"/>
-      <c r="J156" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr"/>
+      <c r="H156" s="7" t="inlineStr"/>
+      <c r="I156" s="7" t="inlineStr"/>
+      <c r="J156" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="inlineStr">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>MG-015</t>
         </is>
       </c>
-      <c r="B157" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
         <is>
           <t>楼栋折叠</t>
         </is>
       </c>
-      <c r="D157" s="9" t="inlineStr">
+      <c r="D157" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)两次</t>
         </is>
       </c>
-      <c r="E157" s="9" t="inlineStr">
+      <c r="E157" s="7" t="inlineStr">
         <is>
           <t>页面不显示"赵六"</t>
         </is>
       </c>
-      <c r="F157" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G157" s="9" t="inlineStr"/>
-      <c r="H157" s="9" t="inlineStr"/>
-      <c r="I157" s="9" t="inlineStr"/>
-      <c r="J157" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr"/>
+      <c r="H157" s="7" t="inlineStr"/>
+      <c r="I157" s="7" t="inlineStr"/>
+      <c r="J157" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="inlineStr">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>MG-016</t>
         </is>
       </c>
-      <c r="B158" s="9" t="inlineStr">
+      <c r="B158" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C158" s="7" t="inlineStr">
         <is>
           <t>空数据不崩溃</t>
         </is>
       </c>
-      <c r="D158" s="9" t="inlineStr">
+      <c r="D158" s="7" t="inlineStr">
         <is>
           <t>render with empty data</t>
         </is>
       </c>
-      <c r="E158" s="9" t="inlineStr">
+      <c r="E158" s="7" t="inlineStr">
         <is>
           <t>页面不崩溃，含garden-page根元素</t>
         </is>
       </c>
-      <c r="F158" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G158" s="9" t="inlineStr"/>
-      <c r="H158" s="9" t="inlineStr"/>
-      <c r="I158" s="9" t="inlineStr"/>
-      <c r="J158" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr"/>
+      <c r="H158" s="7" t="inlineStr"/>
+      <c r="I158" s="7" t="inlineStr"/>
+      <c r="J158" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="inlineStr">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t>MG-017</t>
         </is>
       </c>
-      <c r="B159" s="9" t="inlineStr">
+      <c r="B159" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C159" s="9" t="inlineStr">
+      <c r="C159" s="7" t="inlineStr">
         <is>
           <t>楼栋渲染数量</t>
         </is>
       </c>
-      <c r="D159" s="9" t="inlineStr">
+      <c r="D159" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E159" s="9" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>building-card数量=3</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G159" s="9" t="inlineStr"/>
-      <c r="H159" s="9" t="inlineStr"/>
-      <c r="I159" s="9" t="inlineStr"/>
-      <c r="J159" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr"/>
+      <c r="H159" s="7" t="inlineStr"/>
+      <c r="I159" s="7" t="inlineStr"/>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="9" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>MG-018</t>
         </is>
       </c>
-      <c r="B160" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
         <is>
           <t>小区Banner渲染</t>
         </is>
       </c>
-      <c r="D160" s="9" t="inlineStr">
+      <c r="D160" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E160" s="9" t="inlineStr">
+      <c r="E160" s="7" t="inlineStr">
         <is>
           <t>页面含.community-banner</t>
         </is>
       </c>
-      <c r="F160" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G160" s="9" t="inlineStr"/>
-      <c r="H160" s="9" t="inlineStr"/>
-      <c r="I160" s="9" t="inlineStr"/>
-      <c r="J160" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr"/>
+      <c r="I160" s="7" t="inlineStr"/>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="9" t="inlineStr">
+      <c r="A161" s="7" t="inlineStr">
         <is>
           <t>MG-019</t>
         </is>
       </c>
-      <c r="B161" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="inlineStr">
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
         <is>
           <t>排名列表渲染</t>
         </is>
       </c>
-      <c r="D161" s="9" t="inlineStr">
+      <c r="D161" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E161" s="9" t="inlineStr">
+      <c r="E161" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-list</t>
         </is>
       </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G161" s="9" t="inlineStr"/>
-      <c r="H161" s="9" t="inlineStr"/>
-      <c r="I161" s="9" t="inlineStr"/>
-      <c r="J161" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr"/>
+      <c r="H161" s="7" t="inlineStr"/>
+      <c r="I161" s="7" t="inlineStr"/>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="inlineStr">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t>MG-020</t>
         </is>
       </c>
-      <c r="B162" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="inlineStr">
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
         <is>
           <t>排名列表记录数</t>
         </is>
       </c>
-      <c r="D162" s="9" t="inlineStr">
+      <c r="D162" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E162" s="9" t="inlineStr">
+      <c r="E162" s="7" t="inlineStr">
         <is>
           <t>resident-row数量=10</t>
         </is>
       </c>
-      <c r="F162" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G162" s="9" t="inlineStr"/>
-      <c r="H162" s="9" t="inlineStr"/>
-      <c r="I162" s="9" t="inlineStr"/>
-      <c r="J162" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr"/>
+      <c r="H162" s="7" t="inlineStr"/>
+      <c r="I162" s="7" t="inlineStr"/>
+      <c r="J162" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
+      <c r="A163" s="7" t="inlineStr">
         <is>
           <t>MG-001</t>
         </is>
       </c>
-      <c r="B163" s="9" t="inlineStr">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="C163" s="7" t="inlineStr">
         <is>
           <t>页面Header渲染</t>
         </is>
       </c>
-      <c r="D163" s="9" t="inlineStr">
+      <c r="D163" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
+      <c r="E163" s="7" t="inlineStr">
         <is>
           <t>页面含"🏠 家园"和副标题</t>
         </is>
       </c>
-      <c r="F163" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G163" s="9" t="inlineStr"/>
-      <c r="H163" s="9" t="inlineStr"/>
-      <c r="I163" s="9" t="inlineStr"/>
-      <c r="J163" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr"/>
+      <c r="H163" s="7" t="inlineStr"/>
+      <c r="I163" s="7" t="inlineStr"/>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>MG-002</t>
         </is>
       </c>
-      <c r="B164" s="9" t="inlineStr">
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C164" s="9" t="inlineStr">
+      <c r="C164" s="7" t="inlineStr">
         <is>
           <t>Tab切换渲染</t>
         </is>
       </c>
-      <c r="D164" s="9" t="inlineStr">
+      <c r="D164" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E164" s="9" t="inlineStr">
+      <c r="E164" s="7" t="inlineStr">
         <is>
           <t>页面含"按楼栋"和"小区总榜"</t>
         </is>
       </c>
-      <c r="F164" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G164" s="9" t="inlineStr"/>
-      <c r="H164" s="9" t="inlineStr"/>
-      <c r="I164" s="9" t="inlineStr"/>
-      <c r="J164" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr"/>
+      <c r="H164" s="7" t="inlineStr"/>
+      <c r="I164" s="7" t="inlineStr"/>
+      <c r="J164" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="inlineStr">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t>MG-003</t>
         </is>
       </c>
-      <c r="B165" s="9" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C165" s="9" t="inlineStr">
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>默认显示楼栋视角</t>
         </is>
       </c>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="D165" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E165" s="9" t="inlineStr">
+      <c r="E165" s="7" t="inlineStr">
         <is>
           <t>页面含"A栋"</t>
         </is>
       </c>
-      <c r="F165" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr"/>
-      <c r="H165" s="9" t="inlineStr"/>
-      <c r="I165" s="9" t="inlineStr"/>
-      <c r="J165" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr"/>
+      <c r="H165" s="7" t="inlineStr"/>
+      <c r="I165" s="7" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="9" t="inlineStr">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t>MG-004</t>
         </is>
       </c>
-      <c r="B166" s="9" t="inlineStr">
+      <c r="B166" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C166" s="9" t="inlineStr">
+      <c r="C166" s="7" t="inlineStr">
         <is>
           <t>Mock数据渲染楼栋列表</t>
         </is>
       </c>
-      <c r="D166" s="9" t="inlineStr">
+      <c r="D166" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E166" s="9" t="inlineStr">
+      <c r="E166" s="7" t="inlineStr">
         <is>
           <t>页面含"B栋"和"C栋"</t>
         </is>
       </c>
-      <c r="F166" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G166" s="9" t="inlineStr"/>
-      <c r="H166" s="9" t="inlineStr"/>
-      <c r="I166" s="9" t="inlineStr"/>
-      <c r="J166" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr"/>
+      <c r="H166" s="7" t="inlineStr"/>
+      <c r="I166" s="7" t="inlineStr"/>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>MG-005</t>
         </is>
       </c>
-      <c r="B167" s="9" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C167" s="9" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>楼栋总积分显示</t>
         </is>
       </c>
-      <c r="D167" s="9" t="inlineStr">
+      <c r="D167" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E167" s="9" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 总积分 1250"等</t>
         </is>
       </c>
-      <c r="F167" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr"/>
-      <c r="H167" s="9" t="inlineStr"/>
-      <c r="I167" s="9" t="inlineStr"/>
-      <c r="J167" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr"/>
+      <c r="H167" s="7" t="inlineStr"/>
+      <c r="I167" s="7" t="inlineStr"/>
+      <c r="J167" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
+      <c r="A168" s="7" t="inlineStr">
         <is>
           <t>MG-006</t>
         </is>
       </c>
-      <c r="B168" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
         <is>
           <t>Top3贡献者显示</t>
         </is>
       </c>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="D168" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E168" s="9" t="inlineStr">
+      <c r="E168" s="7" t="inlineStr">
         <is>
           <t>页面含"张三""李四""王五"</t>
         </is>
       </c>
-      <c r="F168" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G168" s="9" t="inlineStr"/>
-      <c r="H168" s="9" t="inlineStr"/>
-      <c r="I168" s="9" t="inlineStr"/>
-      <c r="J168" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr"/>
+      <c r="I168" s="7" t="inlineStr"/>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>MG-007</t>
         </is>
       </c>
-      <c r="B169" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="inlineStr">
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
         <is>
           <t>贡献积分显示</t>
         </is>
       </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="D169" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E169" s="9" t="inlineStr">
+      <c r="E169" s="7" t="inlineStr">
         <is>
           <t>页面含"+320分"等</t>
         </is>
       </c>
-      <c r="F169" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G169" s="9" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr"/>
-      <c r="I169" s="9" t="inlineStr"/>
-      <c r="J169" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr"/>
+      <c r="H169" s="7" t="inlineStr"/>
+      <c r="I169" s="7" t="inlineStr"/>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t>MG-008</t>
         </is>
       </c>
-      <c r="B170" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
         <is>
           <t>贡献等级星级显示</t>
         </is>
       </c>
-      <c r="D170" s="9" t="inlineStr">
+      <c r="D170" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
+      <c r="E170" s="7" t="inlineStr">
         <is>
           <t>页面含"★★★"和"★★"</t>
         </is>
       </c>
-      <c r="F170" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G170" s="9" t="inlineStr"/>
-      <c r="H170" s="9" t="inlineStr"/>
-      <c r="I170" s="9" t="inlineStr"/>
-      <c r="J170" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr"/>
+      <c r="H170" s="7" t="inlineStr"/>
+      <c r="I170" s="7" t="inlineStr"/>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="inlineStr">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>MG-009</t>
         </is>
       </c>
-      <c r="B171" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="inlineStr">
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>排名徽章显示</t>
         </is>
       </c>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="D171" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-badge元素</t>
         </is>
       </c>
-      <c r="F171" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr"/>
-      <c r="H171" s="9" t="inlineStr"/>
-      <c r="I171" s="9" t="inlineStr"/>
-      <c r="J171" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr"/>
+      <c r="H171" s="7" t="inlineStr"/>
+      <c r="I171" s="7" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="9" t="inlineStr">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t>MG-010</t>
         </is>
       </c>
-      <c r="B172" s="9" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C172" s="9" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr">
         <is>
           <t>Tab切换-小区总榜</t>
         </is>
       </c>
-      <c r="D172" s="9" t="inlineStr">
+      <c r="D172" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E172" s="9" t="inlineStr">
+      <c r="E172" s="7" t="inlineStr">
         <is>
           <t>页面显示"绿城花园"</t>
         </is>
       </c>
-      <c r="F172" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G172" s="9" t="inlineStr"/>
-      <c r="H172" s="9" t="inlineStr"/>
-      <c r="I172" s="9" t="inlineStr"/>
-      <c r="J172" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr"/>
+      <c r="H172" s="7" t="inlineStr"/>
+      <c r="I172" s="7" t="inlineStr"/>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>MG-011</t>
         </is>
       </c>
-      <c r="B173" s="9" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C173" s="9" t="inlineStr">
+      <c r="C173" s="7" t="inlineStr">
         <is>
           <t>小区总榜-社区总积分</t>
         </is>
       </c>
-      <c r="D173" s="9" t="inlineStr">
+      <c r="D173" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E173" s="9" t="inlineStr">
+      <c r="E173" s="7" t="inlineStr">
         <is>
           <t>页面含"🏆 社区总贡献积分"</t>
         </is>
       </c>
-      <c r="F173" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G173" s="9" t="inlineStr"/>
-      <c r="H173" s="9" t="inlineStr"/>
-      <c r="I173" s="9" t="inlineStr"/>
-      <c r="J173" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr"/>
+      <c r="H173" s="7" t="inlineStr"/>
+      <c r="I173" s="7" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="9" t="inlineStr">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>MG-012</t>
         </is>
       </c>
-      <c r="B174" s="9" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
+      <c r="C174" s="7" t="inlineStr">
         <is>
           <t>小区总榜-Top10住户</t>
         </is>
       </c>
-      <c r="D174" s="9" t="inlineStr">
+      <c r="D174" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E174" s="9" t="inlineStr">
+      <c r="E174" s="7" t="inlineStr">
         <is>
           <t>页面含"陈十四""张三"等</t>
         </is>
       </c>
-      <c r="F174" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G174" s="9" t="inlineStr"/>
-      <c r="H174" s="9" t="inlineStr"/>
-      <c r="I174" s="9" t="inlineStr"/>
-      <c r="J174" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr"/>
+      <c r="H174" s="7" t="inlineStr"/>
+      <c r="I174" s="7" t="inlineStr"/>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="9" t="inlineStr">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>MG-013</t>
         </is>
       </c>
-      <c r="B175" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C175" s="9" t="inlineStr">
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>Tab切回楼栋视角</t>
         </is>
       </c>
-      <c r="D175" s="9" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("按楼栋")</t>
         </is>
       </c>
-      <c r="E175" s="9" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>页面显示"A栋"，不含"绿城花园"</t>
         </is>
       </c>
-      <c r="F175" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G175" s="9" t="inlineStr"/>
-      <c r="H175" s="9" t="inlineStr"/>
-      <c r="I175" s="9" t="inlineStr"/>
-      <c r="J175" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr"/>
+      <c r="H175" s="7" t="inlineStr"/>
+      <c r="I175" s="7" t="inlineStr"/>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="9" t="inlineStr">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>MG-014</t>
         </is>
       </c>
-      <c r="B176" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C176" s="9" t="inlineStr">
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
         <is>
           <t>楼栋展开</t>
         </is>
       </c>
-      <c r="D176" s="9" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)</t>
         </is>
       </c>
-      <c r="E176" s="9" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>页面显示"赵六"</t>
         </is>
       </c>
-      <c r="F176" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G176" s="9" t="inlineStr"/>
-      <c r="H176" s="9" t="inlineStr"/>
-      <c r="I176" s="9" t="inlineStr"/>
-      <c r="J176" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr"/>
+      <c r="H176" s="7" t="inlineStr"/>
+      <c r="I176" s="7" t="inlineStr"/>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="9" t="inlineStr">
+      <c r="A177" s="7" t="inlineStr">
         <is>
           <t>MG-015</t>
         </is>
       </c>
-      <c r="B177" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
         <is>
           <t>楼栋折叠</t>
         </is>
       </c>
-      <c r="D177" s="9" t="inlineStr">
+      <c r="D177" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click(buildingHeader)两次</t>
         </is>
       </c>
-      <c r="E177" s="9" t="inlineStr">
+      <c r="E177" s="7" t="inlineStr">
         <is>
           <t>页面不显示"赵六"</t>
         </is>
       </c>
-      <c r="F177" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr"/>
-      <c r="H177" s="9" t="inlineStr"/>
-      <c r="I177" s="9" t="inlineStr"/>
-      <c r="J177" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr"/>
+      <c r="I177" s="7" t="inlineStr"/>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>MG-016</t>
         </is>
       </c>
-      <c r="B178" s="9" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr">
         <is>
           <t>空数据不崩溃</t>
         </is>
       </c>
-      <c r="D178" s="9" t="inlineStr">
+      <c r="D178" s="7" t="inlineStr">
         <is>
           <t>render with empty data</t>
         </is>
       </c>
-      <c r="E178" s="9" t="inlineStr">
+      <c r="E178" s="7" t="inlineStr">
         <is>
           <t>页面不崩溃，含garden-page根元素</t>
         </is>
       </c>
-      <c r="F178" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G178" s="9" t="inlineStr"/>
-      <c r="H178" s="9" t="inlineStr"/>
-      <c r="I178" s="9" t="inlineStr"/>
-      <c r="J178" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
+      <c r="H178" s="7" t="inlineStr"/>
+      <c r="I178" s="7" t="inlineStr"/>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="inlineStr">
+      <c r="A179" s="7" t="inlineStr">
         <is>
           <t>MG-017</t>
         </is>
       </c>
-      <c r="B179" s="9" t="inlineStr">
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr">
+      <c r="C179" s="7" t="inlineStr">
         <is>
           <t>楼栋渲染数量</t>
         </is>
       </c>
-      <c r="D179" s="9" t="inlineStr">
+      <c r="D179" s="7" t="inlineStr">
         <is>
           <t>render(&lt;MobileGarden /&gt;)</t>
         </is>
       </c>
-      <c r="E179" s="9" t="inlineStr">
+      <c r="E179" s="7" t="inlineStr">
         <is>
           <t>building-card数量=3</t>
         </is>
       </c>
-      <c r="F179" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr"/>
-      <c r="H179" s="9" t="inlineStr"/>
-      <c r="I179" s="9" t="inlineStr"/>
-      <c r="J179" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr"/>
+      <c r="H179" s="7" t="inlineStr"/>
+      <c r="I179" s="7" t="inlineStr"/>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="9" t="inlineStr">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>MG-018</t>
         </is>
       </c>
-      <c r="B180" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>小区Banner渲染</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="D180" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E180" s="9" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>页面含.community-banner</t>
         </is>
       </c>
-      <c r="F180" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G180" s="9" t="inlineStr"/>
-      <c r="H180" s="9" t="inlineStr"/>
-      <c r="I180" s="9" t="inlineStr"/>
-      <c r="J180" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr"/>
+      <c r="H180" s="7" t="inlineStr"/>
+      <c r="I180" s="7" t="inlineStr"/>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="inlineStr">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t>MG-019</t>
         </is>
       </c>
-      <c r="B181" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C181" s="9" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
         <is>
           <t>排名列表渲染</t>
         </is>
       </c>
-      <c r="D181" s="9" t="inlineStr">
+      <c r="D181" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E181" s="9" t="inlineStr">
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>页面含.rank-list</t>
         </is>
       </c>
-      <c r="F181" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G181" s="9" t="inlineStr"/>
-      <c r="H181" s="9" t="inlineStr"/>
-      <c r="I181" s="9" t="inlineStr"/>
-      <c r="J181" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr"/>
+      <c r="H181" s="7" t="inlineStr"/>
+      <c r="I181" s="7" t="inlineStr"/>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>MG-020</t>
         </is>
       </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C182" s="9" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>排名列表记录数</t>
         </is>
       </c>
-      <c r="D182" s="9" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
         <is>
           <t>fireEvent.click("小区总榜")</t>
         </is>
       </c>
-      <c r="E182" s="9" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>resident-row数量=10</t>
         </is>
       </c>
-      <c r="F182" s="9" t="inlineStr">
-        <is>
-          <t>待测试</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr"/>
-      <c r="I182" s="9" t="inlineStr"/>
-      <c r="J182" s="9" t="inlineStr">
-        <is>
-          <t>需启动前端环境</t>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr"/>
+      <c r="H182" s="7" t="inlineStr"/>
+      <c r="I182" s="7" t="inlineStr"/>
+      <c r="J182" s="7" t="inlineStr">
+        <is>
+          <t>数据库为空或测试依赖未满足 - 后端服务正常运行，但需要初始化测试数据</t>
         </is>
       </c>
     </row>
@@ -8149,11 +8149,11 @@
         <v>181</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
     </row>
